--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N2_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N2_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.58968674485857</v>
+        <v>5.945824096039518</v>
       </c>
       <c r="D2" t="n">
-        <v>36.99801295797256</v>
+        <v>6.012177105670542</v>
       </c>
       <c r="E2" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F2" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.13942324331005</v>
+        <v>3.760156277037884</v>
       </c>
       <c r="D3" t="n">
-        <v>23.07307354681513</v>
+        <v>3.749374451357459</v>
       </c>
       <c r="E3" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F3" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.73919802402827</v>
+        <v>3.045119678904594</v>
       </c>
       <c r="D4" t="n">
-        <v>18.95480676841471</v>
+        <v>3.080156099867391</v>
       </c>
       <c r="E4" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F4" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.52564699741724</v>
+        <v>3.172917637080302</v>
       </c>
       <c r="D5" t="n">
-        <v>19.0796989974618</v>
+        <v>3.100451087087543</v>
       </c>
       <c r="E5" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F5" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.22329957203934</v>
+        <v>3.611286180456392</v>
       </c>
       <c r="D6" t="n">
-        <v>22.14204517607484</v>
+        <v>3.598082341112161</v>
       </c>
       <c r="E6" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F6" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.33837701867336</v>
+        <v>4.929986265534422</v>
       </c>
       <c r="D7" t="n">
-        <v>29.86443118467277</v>
+        <v>4.852970067509326</v>
       </c>
       <c r="E7" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F7" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.32659563060553</v>
+        <v>3.303071789973398</v>
       </c>
       <c r="D8" t="n">
-        <v>19.99670821163376</v>
+        <v>3.249465084390486</v>
       </c>
       <c r="E8" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F8" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.94083728675699</v>
+        <v>5.51538605909801</v>
       </c>
       <c r="D9" t="n">
-        <v>33.97908633497511</v>
+        <v>5.521601529433457</v>
       </c>
       <c r="E9" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F9" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.94987690781685</v>
+        <v>3.729354997520239</v>
       </c>
       <c r="D10" t="n">
-        <v>22.8214016717602</v>
+        <v>3.708477771661032</v>
       </c>
       <c r="E10" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F10" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.46852998085882</v>
+        <v>5.276136121889558</v>
       </c>
       <c r="D11" t="n">
-        <v>2.904300456670601</v>
+        <v>0.4719488242089727</v>
       </c>
       <c r="E11" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F11" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.96002661280026</v>
+        <v>6.493504324580043</v>
       </c>
       <c r="D12" t="n">
-        <v>40.13645048880625</v>
+        <v>6.522173204431017</v>
       </c>
       <c r="E12" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F12" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.89028904817728</v>
+        <v>4.694671970328808</v>
       </c>
       <c r="D13" t="n">
-        <v>29.12301889756349</v>
+        <v>4.732490570854067</v>
       </c>
       <c r="E13" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F13" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.84375812962796</v>
+        <v>3.712110696064543</v>
       </c>
       <c r="D14" t="n">
-        <v>13.60147050873544</v>
+        <v>2.21023895766951</v>
       </c>
       <c r="E14" t="n">
-        <v>6.752178809223891</v>
+        <v>1.097229056498882</v>
       </c>
       <c r="F14" t="n">
-        <v>9.663831609062692</v>
+        <v>1.570372636472688</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
